--- a/branches_1.xlsx
+++ b/branches_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\EdioD\PycharmProjects\variacao-tensao-frp\13Bus\23742222\pyomo_data\model_reg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AD95A2-CA2C-42C9-907E-BEB7A1CBDA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E639562-6316-4308-B1A2-CEC069BB10B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4413,7 +4413,7 @@
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
         <v>82</v>
@@ -4469,7 +4469,7 @@
         <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>633</v>
@@ -4525,7 +4525,7 @@
         <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>675</v>
@@ -4581,7 +4581,7 @@
         <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>675</v>
@@ -4637,7 +4637,7 @@
         <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>680</v>
@@ -4693,7 +4693,7 @@
         <v>135</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>671</v>
@@ -5081,6 +5081,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
